--- a/data/pdedata.xlsx
+++ b/data/pdedata.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,9 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -46,7 +49,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -76,11 +79,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -105,6 +114,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8548,91 +8560,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P113"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>num_lines</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>num_char</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>pde_class</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>phys_process</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>phys_valid</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>num_method</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>corruption_source_id</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>corruption_source_pde</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>injected_comments</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>delta_comments</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>num_comments</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>gt_sample</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>mod_type</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>foobar_vars</t>
         </is>
       </c>
     </row>
@@ -8780,11 +8787,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8913,11 +8915,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9024,11 +9021,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9125,11 +9117,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9218,11 +9205,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9317,11 +9299,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9413,11 +9390,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9511,11 +9483,6 @@
       <c r="O9" t="inlineStr">
         <is>
           <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -9611,11 +9578,6 @@
       <c r="O10" t="inlineStr">
         <is>
           <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -9720,11 +9682,6 @@
       <c r="O11" t="inlineStr">
         <is>
           <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -9814,11 +9771,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9892,11 +9844,6 @@
       <c r="O13" t="inlineStr">
         <is>
           <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -10039,11 +9986,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10167,11 +10109,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10273,11 +10210,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10369,11 +10301,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10457,11 +10384,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10551,11 +10473,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10642,11 +10559,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10736,11 +10648,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10828,11 +10735,6 @@
       <c r="O22" t="inlineStr">
         <is>
           <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -10952,11 +10854,6 @@
       <c r="O23" t="inlineStr">
         <is>
           <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -11055,11 +10952,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11141,11 +11033,6 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -11293,11 +11180,6 @@
       <c r="O26" t="inlineStr">
         <is>
           <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -11497,11 +11379,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11648,11 +11525,6 @@
       <c r="O28" t="inlineStr">
         <is>
           <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -11884,11 +11756,6 @@
           <t>Comm_Valid</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12027,11 +11894,6 @@
       <c r="O30" t="inlineStr">
         <is>
           <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -12226,11 +12088,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12368,11 +12225,6 @@
       <c r="O32" t="inlineStr">
         <is>
           <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -12597,11 +12449,6 @@
           <t>NoComm_Valid</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12690,11 +12537,6 @@
       <c r="O34" t="inlineStr">
         <is>
           <t>NoComm_InValid</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -12837,11 +12679,6 @@
           <t>NoComm_InValid</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12965,11 +12802,6 @@
           <t>NoComm_InValid</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -13071,11 +12903,6 @@
           <t>NoComm_InValid</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13159,11 +12986,6 @@
           <t>NoComm_InValid</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13253,11 +13075,6 @@
           <t>NoComm_InValid</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13344,11 +13161,6 @@
           <t>NoComm_InValid</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13436,11 +13248,6 @@
       <c r="O41" t="inlineStr">
         <is>
           <t>NoComm_InValid</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -13530,11 +13337,6 @@
       <c r="O42" t="inlineStr">
         <is>
           <t>NoComm_InValid</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -13658,11 +13460,6 @@
       <c r="O43" t="inlineStr">
         <is>
           <t>NoComm_InValid</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -13761,11 +13558,6 @@
           <t>NoComm_InValid</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -13847,11 +13639,6 @@
       <c r="O45" t="inlineStr">
         <is>
           <t>NoComm_InValid</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -13992,11 +13779,6 @@
       <c r="O46" t="inlineStr">
         <is>
           <t>NoComm_InValid</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -14191,11 +13973,6 @@
           <t>NoComm_InValid</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14333,11 +14110,6 @@
       <c r="O48" t="inlineStr">
         <is>
           <t>NoComm_InValid</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -14562,11 +14334,6 @@
           <t>NoComm_InValid</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14726,11 +14493,6 @@
           <t>CorrComm</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14873,11 +14635,6 @@
           <t>CorrComm</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -14998,11 +14755,6 @@
           <t>CorrComm</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15111,11 +14863,6 @@
       <c r="O53" t="inlineStr">
         <is>
           <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -15218,11 +14965,6 @@
       <c r="O54" t="inlineStr">
         <is>
           <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -15333,11 +15075,6 @@
           <t>CorrComm</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -15443,11 +15180,6 @@
           <t>CorrComm</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15555,11 +15287,6 @@
       <c r="O57" t="inlineStr">
         <is>
           <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -15669,11 +15396,6 @@
       <c r="O58" t="inlineStr">
         <is>
           <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -15792,11 +15514,6 @@
       <c r="O59" t="inlineStr">
         <is>
           <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -15900,11 +15617,6 @@
           <t>CorrComm</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15992,11 +15704,6 @@
       <c r="O61" t="inlineStr">
         <is>
           <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -16158,11 +15865,6 @@
       <c r="O62" t="inlineStr">
         <is>
           <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -16376,11 +16078,6 @@
           <t>CorrComm</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -16541,11 +16238,6 @@
       <c r="O64" t="inlineStr">
         <is>
           <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -16791,11 +16483,6 @@
           <t>CorrComm</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16866,13 +16553,13 @@
         foobar_30[:, 0] = 0\n
         foobar_30[:, -1] = 0\n
     elif foobar_18 == 2:\n
-        foobar_23, foobar_24 = (0, 0)\n
+        (foobar_23, foobar_24) = (0, 0)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 + 1]) * (foobar_28[foobar_23, foobar_24 + 1] - foobar_28[foobar_23, foobar_24])\n
-        foobar_23, foobar_24 = (0, foobar_12)\n
+        (foobar_23, foobar_24) = (0, foobar_12)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
-        foobar_23, foobar_24 = (foobar_11, 0)\n
+        (foobar_23, foobar_24) = (foobar_11, 0)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 + 1]) * (foobar_28[foobar_23, foobar_24 + 1] - foobar_28[foobar_23, foobar_24])\n
-        foobar_23, foobar_24 = (foobar_11, foobar_12)\n
+        (foobar_23, foobar_24) = (foobar_11, foobar_12)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
         foobar_23 = 0\n
         foobar_30[foobar_23, 1:foobar_12 - 1] = 2 * foobar_28[foobar_23, 1:foobar_12 - 1] - (foobar_28[foobar_23, 1:foobar_12 - 1] - 2 * foobar_20 * foobar_15[foobar_23, 1:foobar_12 - 1]) + foobar_5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23 + 1, 1:foobar_12 - 1]) * (foobar_28[foobar_23 + 1, 1:foobar_12 - 1] - foobar_28[foobar_23, 1:foobar_12 - 1]) + foobar_6 * (0.5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23, 2:foobar_12]) * (foobar_28[foobar_23, 2:foobar_12] - foobar_28[foobar_23, 1:foobar_12 - 1]) - 0.5 * (foobar_27[foobar_23, 0:foobar_12 - 2] + foobar_27[foobar_23, 1:foobar_12 - 1]) * (foobar_28[foobar_23, 1:foobar_12 - 1] - foobar_28[foobar_23, 0:foobar_12 - 2]))\n
@@ -16902,13 +16589,13 @@
             foobar_30[:, 0] = 0\n
             foobar_30[:, -1] = 0\n
         elif foobar_18 == 2:\n
-            foobar_23, foobar_24 = (0, 0)\n
+            (foobar_23, foobar_24) = (0, 0)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 + 1]) * (foobar_28[foobar_23, foobar_24 + 1] - foobar_28[foobar_23, foobar_24])\n
-            foobar_23, foobar_24 = (0, foobar_12)\n
+            (foobar_23, foobar_24) = (0, foobar_12)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
-            foobar_23, foobar_24 = (foobar_11, 0)\n
+            (foobar_23, foobar_24) = (foobar_11, 0)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
-            foobar_23, foobar_24 = (foobar_11, foobar_12)\n
+            (foobar_23, foobar_24) = (foobar_11, foobar_12)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
             foobar_23 = 0\n
             foobar_30[foobar_23, 1:foobar_12 - 1] = 2 * foobar_28[foobar_23, 1:foobar_12 - 1] - foobar_29[foobar_23, 1:foobar_12 - 1] + foobar_5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23 + 1, 1:foobar_12 - 1]) * (foobar_28[foobar_23 + 1, 1:foobar_12 - 1] - foobar_28[foobar_23, 1:foobar_12 - 1]) + foobar_6 * (0.5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23, 2:foobar_12]) * (foobar_28[foobar_23, 2:foobar_12] - foobar_28[foobar_23, 1:foobar_12 - 1]) - 0.5 * (foobar_27[foobar_23, 0:foobar_12 - 2] + foobar_27[foobar_23, foobar_24]) * (foobar_28[foobar_23, 1:foobar_12 - 1] - foobar_28[foobar_23, 0:foobar_12 - 2]))\n
@@ -16936,7 +16623,7 @@
         <v>125</v>
       </c>
       <c r="D66" t="n">
-        <v>16198</v>
+        <v>16214</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -16970,12 +16657,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17104,12 +16786,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17200,12 +16877,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17243,14 +16915,14 @@
     foobar_20 = np.linspace(0, foobar_3, foobar_4, endpoint=False)\n
     foobar_15 = np.exp(-50 * (foobar_20 - foobar_3 / 2) ** 2)\n
     foobar_18 = np.zeros_like(foobar_20)\n
-    foobar_20, foobar_12, foobar_10 = fn1(foobar_15, foobar_18, foobar_3, T=5, dt=0.05, c=foobar_6)</t>
+    (foobar_20, foobar_12, foobar_10) = fn1(foobar_15, foobar_18, foobar_3, T=5, dt=0.05, c=foobar_6)</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>27</v>
       </c>
       <c r="D69" t="n">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -17284,12 +16956,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17364,12 +17031,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17449,12 +17111,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17532,12 +17189,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17617,12 +17269,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17702,12 +17349,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17796,12 +17438,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17874,12 +17511,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -17943,12 +17575,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18021,13 +17648,13 @@
         foobar_30[:, 0] = 0\n
         foobar_30[:, -1] = 0\n
     elif foobar_18 == 2:\n
-        foobar_23, foobar_24 = (0, 0)\n
+        (foobar_23, foobar_24) = (0, 0)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 + 1]) * (foobar_28[foobar_23, foobar_24 + 1] - foobar_28[foobar_23, foobar_24])\n
-        foobar_23, foobar_24 = (0, foobar_12)\n
+        (foobar_23, foobar_24) = (0, foobar_12)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
-        foobar_23, foobar_24 = (foobar_11, 0)\n
+        (foobar_23, foobar_24) = (foobar_11, 0)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 + 1]) * (foobar_28[foobar_23, foobar_24 + 1] - foobar_28[foobar_23, foobar_24])\n
-        foobar_23, foobar_24 = (foobar_11, foobar_12)\n
+        (foobar_23, foobar_24) = (foobar_11, foobar_12)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
         foobar_23 = 0\n
         foobar_30[foobar_23, 1:foobar_12 - 1] = 2 * foobar_28[foobar_23, 1:foobar_12 - 1] - (foobar_28[foobar_23, 1:foobar_12 - 1] - 2 * foobar_20 * foobar_15[foobar_23, 1:foobar_12 - 1]) + foobar_5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23 + 1, 1:foobar_12 - 1]) * (foobar_28[foobar_23 + 1, 1:foobar_12 - 1] - foobar_28[foobar_23, 1:foobar_12 - 1]) + foobar_6 * (0.5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23, 2:foobar_12]) * (foobar_28[foobar_23, 2:foobar_12] - foobar_28[foobar_23, 1:foobar_12 - 1]) - 0.5 * (foobar_27[foobar_23, 0:foobar_12 - 2] + foobar_27[foobar_23, 1:foobar_12 - 1]) * (foobar_28[foobar_23, 1:foobar_12 - 1] - foobar_28[foobar_23, 0:foobar_12 - 2]))\n
@@ -18057,13 +17684,13 @@
             foobar_30[:, 0] = 0\n
             foobar_30[:, -1] = 0\n
         elif foobar_18 == 2:\n
-            foobar_23, foobar_24 = (0, 0)\n
+            (foobar_23, foobar_24) = (0, 0)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 + 1]) * (foobar_28[foobar_23, foobar_24 + 1] - foobar_28[foobar_23, foobar_24])\n
-            foobar_23, foobar_24 = (0, foobar_12)\n
+            (foobar_23, foobar_24) = (0, foobar_12)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
-            foobar_23, foobar_24 = (foobar_11, 0)\n
+            (foobar_23, foobar_24) = (foobar_11, 0)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
-            foobar_23, foobar_24 = (foobar_11, foobar_12)\n
+            (foobar_23, foobar_24) = (foobar_11, foobar_12)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
             foobar_23 = 0\n
             foobar_30[foobar_23, 1:foobar_12 - 1] = 2 * foobar_28[foobar_23, 1:foobar_12 - 1] - foobar_29[foobar_23, 1:foobar_12 - 1] + foobar_5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23 + 1, 1:foobar_12 - 1]) * (foobar_28[foobar_23 + 1, 1:foobar_12 - 1] - foobar_28[foobar_23, 1:foobar_12 - 1]) + foobar_6 * (0.5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23, 2:foobar_12]) * (foobar_28[foobar_23, 2:foobar_12] - foobar_28[foobar_23, 1:foobar_12 - 1]) - 0.5 * (foobar_27[foobar_23, 0:foobar_12 - 2] + foobar_27[foobar_23, foobar_24]) * (foobar_28[foobar_23, 1:foobar_12 - 1] - foobar_28[foobar_23, 0:foobar_12 - 2]))\n
@@ -18091,7 +17718,7 @@
         <v>125</v>
       </c>
       <c r="D78" t="n">
-        <v>16198</v>
+        <v>16214</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -18125,12 +17752,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18259,12 +17881,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18355,12 +17972,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18398,14 +18010,14 @@
     foobar_20 = np.linspace(0, foobar_3, foobar_4, endpoint=False)\n
     foobar_15 = np.exp(-50 * (foobar_20 - foobar_3 / 2) ** 2)\n
     foobar_18 = np.zeros_like(foobar_20)\n
-    foobar_20, foobar_12, foobar_10 = fn1(foobar_15, foobar_18, foobar_3, T=5, dt=0.05, c=foobar_6)</t>
+    (foobar_20, foobar_12, foobar_10) = fn1(foobar_15, foobar_18, foobar_3, T=5, dt=0.05, c=foobar_6)</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>27</v>
       </c>
       <c r="D81" t="n">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -18439,12 +18051,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18519,12 +18126,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18604,12 +18206,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18687,12 +18284,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18771,12 +18363,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18855,12 +18442,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -18967,12 +18549,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -19055,12 +18632,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -19134,12 +18706,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -19163,7 +18730,7 @@
 foobar_7 = 2 / (foobar_13 - 1)\n
 foobar_22 = numpy.linspace(0, 2, foobar_12)\n
 foobar_23 = numpy.linspace(0, 2, foobar_13)\n
-foobar_1, foobar_2 = numpy.meshgrid(foobar_22, foobar_23)\n
+(foobar_1, foobar_2) = numpy.meshgrid(foobar_22, foobar_23)\n
 foobar_17 = 1\n
 foobar_11 = 0.1\n
 foobar_5 = 0.001\n
@@ -19213,14 +18780,14 @@
 foobar_14 = numpy.zeros((foobar_13, foobar_12))\n
 foobar_3 = numpy.zeros((foobar_13, foobar_12))\n
 foobar_10 = 700\n
-foobar_18, foobar_20, foobar_14 = fn3(foobar_10, foobar_18, foobar_20, foobar_5, foobar_6, foobar_7, foobar_14, foobar_17, foobar_11)</t>
+(foobar_18, foobar_20, foobar_14) = fn3(foobar_10, foobar_18, foobar_20, foobar_5, foobar_6, foobar_7, foobar_14, foobar_17, foobar_11)</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>63</v>
       </c>
       <c r="D90" t="n">
-        <v>4214</v>
+        <v>4218</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -19254,12 +18821,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -19300,7 +18862,7 @@
 foobar_8 = 2 / (foobar_13 - 1)\n
 foobar_24 = numpy.linspace(0, 2, foobar_12)\n
 foobar_25 = numpy.linspace(0, 2, foobar_13)\n
-foobar_2, foobar_3 = numpy.meshgrid(foobar_24, foobar_25)\n
+(foobar_2, foobar_3) = numpy.meshgrid(foobar_24, foobar_25)\n
 foobar_17 = 1\n
 foobar_11 = 0.1\n
 foobar_1 = 1\n
@@ -19337,7 +18899,7 @@
         <v>60</v>
       </c>
       <c r="D91" t="n">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -19371,12 +18933,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -19416,7 +18973,7 @@
 def fn1(foobar_1, foobar_7):\n
     foobar_19 = np.ogrid[foobar_1.local_slice(False)]\n
     foobar_10 = foobar_1.global_shape()\n
-    foobar_19 = [np.broadcast_to(foobar_39 * foobar_7[foobar_26] / foobar_10[foobar_26], foobar_1.shape(False)) for foobar_26, foobar_39 in enumerate(foobar_19)]\n
+    foobar_19 = [np.broadcast_to(foobar_39 * foobar_7[foobar_26] / foobar_10[foobar_26], foobar_1.shape(False)) for (foobar_26, foobar_39) in enumerate(foobar_19)]\n
     return foobar_19\n
 \n
 def fn2(foobar_1, foobar_7):\n
@@ -19424,10 +18981,10 @@
     foobar_10 = foobar_1.global_shape()\n
     foobar_28 = [np.fft.fftfreq(foobar_30, 1.0 / foobar_30).astype(int) for foobar_30 in foobar_10[:-1]]\n
     foobar_28.append(np.fft.rfftfreq(foobar_10[-1], 1.0 / foobar_10[-1]).astype(int))\n
-    foobar_3 = [foobar_29[foobar_35] for foobar_29, foobar_35 in zip(foobar_28, foobar_34)]\n
+    foobar_3 = [foobar_29[foobar_35] for (foobar_29, foobar_35) in zip(foobar_28, foobar_34)]\n
     foobar_6 = np.meshgrid(*foobar_3, indexing='ij', sparse=True)\n
     foobar_8 = 2 * np.pi / foobar_7\n
-    return [np.broadcast_to(foobar_28 * foobar_8[foobar_26], foobar_1.shape(True)) for foobar_26, foobar_28 in enumerate(foobar_6)]\n
+    return [np.broadcast_to(foobar_28 * foobar_8[foobar_26], foobar_1.shape(True)) for (foobar_26, foobar_28) in enumerate(foobar_6)]\n
 foobar_19 = fn1(foobar_1, foobar_7)\n
 foobar_3 = fn2(foobar_1, foobar_7)\n
 foobar_3 = np.array(foobar_3).astype(float)\n
@@ -19486,7 +19043,7 @@
         <v>92</v>
       </c>
       <c r="D92" t="n">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -19520,12 +19077,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -19568,15 +19120,15 @@
 def fn4(foobar_27, foobar_1, foobar_2, foobar_33, foobar_45=4):\n
     foobar_23 = grids.Grid((foobar_1, foobar_2), domain=((0, 2 * jnp.pi), (0, 2 * jnp.pi)))\n
     foobar_56 = initial_conditions.filtered_velocity_field(foobar_27, foobar_23, maximum_velocity=foobar_33, peak_wavenumber=foobar_45)\n
-    foobar_59, foobar_61 = (foobar_56[0].data, foobar_56[1].data)\n
-    foobar_29, foobar_30 = fn1(foobar_1, foobar_2)\n
+    (foobar_59, foobar_61) = (foobar_56[0].data, foobar_56[1].data)\n
+    (foobar_29, foobar_30) = fn1(foobar_1, foobar_2)\n
     foobar_60 = jnp.fft.rfftn(foobar_59)\n
     foobar_62 = jnp.fft.rfftn(foobar_61)\n
     foobar_42 = 2j * jnp.pi * (foobar_29 * foobar_62 - foobar_30 * foobar_60)\n
     return jnp.fft.irfftn(foobar_42, s=(foobar_1, foobar_2))\n
 \n
 def fn5(foobar_58, foobar_29, foobar_30, foobar_16, foobar_1, foobar_2):\n
-    foobar_60, foobar_62 = fn3(foobar_58, foobar_29, foobar_30)\n
+    (foobar_60, foobar_62) = fn3(foobar_58, foobar_29, foobar_30)\n
     foobar_59 = jnp.fft.irfftn(foobar_60, s=(foobar_1, foobar_2))\n
     foobar_61 = jnp.fft.irfftn(foobar_62, s=(foobar_1, foobar_2))\n
     foobar_20 = 2j * jnp.pi * foobar_29 * foobar_58\n
@@ -19606,26 +19158,26 @@
     foobar_49 = jnp.array(foobar_48)\n
     foobar_15 = foobar_49[1] - foobar_49[0]\n
     foobar_36 = len(foobar_49) - 1\n
-    foobar_29, foobar_30 = fn1(foobar_1, foobar_2)\n
+    (foobar_29, foobar_30) = fn1(foobar_1, foobar_2)\n
     foobar_16 = fn2(foobar_1, foobar_2)\n
     foobar_31 = (2j * jnp.pi) ** 2 * (foobar_29 ** 2 + foobar_30 ** 2)\n
     foobar_32 = foobar_57 * foobar_31 - foobar_14\n
-    foobar_27, foobar_26 = random.split(foobar_27)\n
+    (foobar_27, foobar_26) = random.split(foobar_27)\n
     foobar_40 = foobar_17 if foobar_17 is not None else fn4(foobar_26, foobar_1, foobar_2, foobar_33)\n
     foobar_41 = jnp.fft.rfftn(foobar_40)\n
     foobar_47 = foobar_36 // (foobar_50 - 1)\n
 \n
     def fn9(foobar_12, foobar_5):\n
-        foobar_42, foobar_27 = foobar_12\n
+        (foobar_42, foobar_27) = foobar_12\n
 \n
         def fn10(foobar_12, foobar_5):\n
-            foobar_42, foobar_27 = foobar_12\n
-            foobar_27, foobar_5 = random.split(foobar_27)\n
+            (foobar_42, foobar_27) = foobar_12\n
+            (foobar_27, foobar_5) = random.split(foobar_27)\n
             foobar_43 = fn6(foobar_42, foobar_29, foobar_30, foobar_16, foobar_1, foobar_2, foobar_32, foobar_15)\n
             return ((foobar_43, foobar_27), None)\n
-        (foobar_43, foobar_27), foobar_5 = lax.scan(fn10, (foobar_42, foobar_27), None, length=foobar_47)\n
+        ((foobar_43, foobar_27), foobar_5) = lax.scan(fn10, (foobar_42, foobar_27), None, length=foobar_47)\n
         return ((foobar_43, foobar_27), foobar_43)\n
-    (foobar_5, foobar_5), foobar_53 = lax.scan(fn9, (foobar_41, foobar_27), None, length=foobar_50 - 1)\n
+    ((foobar_5, foobar_5), foobar_53) = lax.scan(fn9, (foobar_41, foobar_27), None, length=foobar_50 - 1)\n
     foobar_53 = jnp.concatenate([foobar_41[None], foobar_53], axis=0)\n
     if foobar_51 is not None and foobar_51 != foobar_1:\n
         foobar_3 = foobar_51\n
@@ -19657,7 +19209,7 @@
         <v>114</v>
       </c>
       <c r="D93" t="n">
-        <v>6739</v>
+        <v>6759</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -19691,12 +19243,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Comm_Valid</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19267,7 @@
 foobar_7 = 2 / (foobar_13 - 1)\n
 foobar_22 = numpy.linspace(0, 2, foobar_12)\n
 foobar_23 = numpy.linspace(0, 2, foobar_13)\n
-foobar_1, foobar_2 = numpy.meshgrid(foobar_22, foobar_23)\n
+(foobar_1, foobar_2) = numpy.meshgrid(foobar_22, foobar_23)\n
 foobar_17 = 1\n
 foobar_11 = 0.1\n
 foobar_5 = 0.001\n
@@ -19770,14 +19317,14 @@
 foobar_14 = numpy.zeros((foobar_13, foobar_12))\n
 foobar_3 = numpy.zeros((foobar_13, foobar_12))\n
 foobar_10 = 700\n
-foobar_18, foobar_20, foobar_14 = fn3(foobar_10, foobar_18, foobar_20, foobar_5, foobar_6, foobar_7, foobar_14, foobar_17, foobar_11)</t>
+(foobar_18, foobar_20, foobar_14) = fn3(foobar_10, foobar_18, foobar_20, foobar_5, foobar_6, foobar_7, foobar_14, foobar_17, foobar_11)</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>63</v>
       </c>
       <c r="D94" t="n">
-        <v>4214</v>
+        <v>4218</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -19811,12 +19358,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -19858,7 +19400,7 @@
 foobar_8 = 2 / (foobar_13 - 1)\n
 foobar_24 = numpy.linspace(0, 2, foobar_12)\n
 foobar_25 = numpy.linspace(0, 2, foobar_13)\n
-foobar_2, foobar_3 = numpy.meshgrid(foobar_24, foobar_25)\n
+(foobar_2, foobar_3) = numpy.meshgrid(foobar_24, foobar_25)\n
 foobar_17 = 1\n
 foobar_11 = 0.1\n
 foobar_1 = 1\n
@@ -19895,7 +19437,7 @@
         <v>61</v>
       </c>
       <c r="D95" t="n">
-        <v>7159</v>
+        <v>7161</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -19929,12 +19471,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -19974,7 +19511,7 @@
 def fn1(foobar_1, foobar_7):\n
     foobar_19 = np.ogrid[foobar_1.local_slice(False)]\n
     foobar_10 = foobar_1.global_shape()\n
-    foobar_19 = [np.broadcast_to(foobar_39 * foobar_7[foobar_26] / foobar_10[foobar_26], foobar_1.shape(False)) for foobar_26, foobar_39 in enumerate(foobar_19)]\n
+    foobar_19 = [np.broadcast_to(foobar_39 * foobar_7[foobar_26] / foobar_10[foobar_26], foobar_1.shape(False)) for (foobar_26, foobar_39) in enumerate(foobar_19)]\n
     return foobar_19\n
 \n
 def fn2(foobar_1, foobar_7):\n
@@ -19982,10 +19519,10 @@
     foobar_10 = foobar_1.global_shape()\n
     foobar_28 = [np.fft.fftfreq(foobar_30, 1.0 / foobar_30).astype(int) for foobar_30 in foobar_10[:-1]]\n
     foobar_28.append(np.fft.rfftfreq(foobar_10[-1], 1.0 / foobar_10[-1]).astype(int))\n
-    foobar_3 = [foobar_29[foobar_35] for foobar_29, foobar_35 in zip(foobar_28, foobar_34)]\n
+    foobar_3 = [foobar_29[foobar_35] for (foobar_29, foobar_35) in zip(foobar_28, foobar_34)]\n
     foobar_6 = np.meshgrid(*foobar_3, indexing='ij', sparse=True)\n
     foobar_8 = 2 * np.pi / foobar_7\n
-    return [np.broadcast_to(foobar_28 * foobar_8[foobar_26], foobar_1.shape(True)) for foobar_26, foobar_28 in enumerate(foobar_6)]\n
+    return [np.broadcast_to(foobar_28 * foobar_8[foobar_26], foobar_1.shape(True)) for (foobar_26, foobar_28) in enumerate(foobar_6)]\n
 foobar_19 = fn1(foobar_1, foobar_7)\n
 foobar_3 = fn2(foobar_1, foobar_7)\n
 foobar_3 = np.array(foobar_3).astype(float)\n
@@ -20044,7 +19581,7 @@
         <v>92</v>
       </c>
       <c r="D96" t="n">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -20078,12 +19615,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -20126,15 +19658,15 @@
 def fn4(foobar_27, foobar_1, foobar_2, foobar_33, foobar_45=4):\n
     foobar_23 = grids.Grid((foobar_1, foobar_2), domain=((0, 2 * jnp.pi), (0, 2 * jnp.pi)))\n
     foobar_56 = initial_conditions.filtered_velocity_field(foobar_27, foobar_23, maximum_velocity=foobar_33, peak_wavenumber=foobar_45)\n
-    foobar_59, foobar_61 = (foobar_56[0].data, foobar_56[1].data)\n
-    foobar_29, foobar_30 = fn1(foobar_1, foobar_2)\n
+    (foobar_59, foobar_61) = (foobar_56[0].data, foobar_56[1].data)\n
+    (foobar_29, foobar_30) = fn1(foobar_1, foobar_2)\n
     foobar_60 = jnp.fft.rfftn(foobar_59)\n
     foobar_62 = jnp.fft.rfftn(foobar_61)\n
     foobar_42 = 2j * jnp.pi * (foobar_29 * foobar_62 - foobar_30 * foobar_60)\n
     return jnp.fft.irfftn(foobar_42, s=(foobar_1, foobar_2))\n
 \n
 def fn5(foobar_58, foobar_29, foobar_30, foobar_16, foobar_1, foobar_2):\n
-    foobar_60, foobar_62 = fn3(foobar_58, foobar_29, foobar_30)\n
+    (foobar_60, foobar_62) = fn3(foobar_58, foobar_29, foobar_30)\n
     foobar_59 = jnp.fft.irfftn(foobar_60, s=(foobar_1, foobar_2))\n
     foobar_61 = jnp.fft.irfftn(foobar_62, s=(foobar_1, foobar_2))\n
     foobar_20 = 2j * jnp.pi * foobar_29 * foobar_58\n
@@ -20164,26 +19696,26 @@
     foobar_49 = jnp.array(foobar_48)\n
     foobar_15 = foobar_49[1] - foobar_49[0]\n
     foobar_36 = len(foobar_49) - 1\n
-    foobar_29, foobar_30 = fn1(foobar_1, foobar_2)\n
+    (foobar_29, foobar_30) = fn1(foobar_1, foobar_2)\n
     foobar_16 = fn2(foobar_1, foobar_2)\n
     foobar_31 = (2j * jnp.pi) ** 2 * (foobar_29 ** 2 + foobar_30 ** 2)\n
     foobar_32 = foobar_57 * foobar_31 - foobar_14\n
-    foobar_27, foobar_26 = random.split(foobar_27)\n
+    (foobar_27, foobar_26) = random.split(foobar_27)\n
     foobar_40 = foobar_17 if foobar_17 is not None else fn4(foobar_26, foobar_1, foobar_2, foobar_33)\n
     foobar_41 = jnp.fft.rfftn(foobar_40)\n
     foobar_47 = foobar_36 // (foobar_50 - 1)\n
 \n
     def fn9(foobar_12, foobar_5):\n
-        foobar_42, foobar_27 = foobar_12\n
+        (foobar_42, foobar_27) = foobar_12\n
 \n
         def fn10(foobar_12, foobar_5):\n
-            foobar_42, foobar_27 = foobar_12\n
-            foobar_27, foobar_5 = random.split(foobar_27)\n
+            (foobar_42, foobar_27) = foobar_12\n
+            (foobar_27, foobar_5) = random.split(foobar_27)\n
             foobar_43 = fn6(foobar_42, foobar_29, foobar_30, foobar_16, foobar_1, foobar_2, foobar_32, foobar_15)\n
             return ((foobar_43, foobar_27), None)\n
-        (foobar_43, foobar_27), foobar_5 = lax.scan(fn10, (foobar_42, foobar_27), None, length=foobar_47)\n
+        ((foobar_43, foobar_27), foobar_5) = lax.scan(fn10, (foobar_42, foobar_27), None, length=foobar_47)\n
         return ((foobar_43, foobar_27), foobar_43)\n
-    (foobar_5, foobar_5), foobar_53 = lax.scan(fn9, (foobar_41, foobar_27), None, length=foobar_50 - 1)\n
+    ((foobar_5, foobar_5), foobar_53) = lax.scan(fn9, (foobar_41, foobar_27), None, length=foobar_50 - 1)\n
     foobar_53 = jnp.concatenate([foobar_41[None], foobar_53], axis=0)\n
     if foobar_51 is not None and foobar_51 != foobar_1:\n
         foobar_3 = foobar_51\n
@@ -20215,7 +19747,7 @@
         <v>114</v>
       </c>
       <c r="D97" t="n">
-        <v>6739</v>
+        <v>6759</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -20249,12 +19781,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>NoComm_Valid</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -20327,13 +19854,13 @@
         foobar_30[:, 0] = 0\n
         foobar_30[:, -1] = 0\n
     elif foobar_18 == 2:\n
-        foobar_23, foobar_24 = (0, 0)\n
+        (foobar_23, foobar_24) = (0, 0)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 + 1]) * (foobar_28[foobar_23, foobar_24 + 1] - foobar_28[foobar_23, foobar_24])\n
-        foobar_23, foobar_24 = (0, foobar_12)\n
+        (foobar_23, foobar_24) = (0, foobar_12)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
-        foobar_23, foobar_24 = (foobar_11, 0)\n
+        (foobar_23, foobar_24) = (foobar_11, 0)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 + 1]) * (foobar_28[foobar_23, foobar_24 + 1] - foobar_28[foobar_23, foobar_24])\n
-        foobar_23, foobar_24 = (foobar_11, foobar_12)\n
+        (foobar_23, foobar_24) = (foobar_11, foobar_12)\n
         foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - (foobar_28[foobar_23, foobar_24] - 2 * foobar_20 * foobar_15[foobar_23, foobar_24]) + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
         foobar_23 = 0\n
         foobar_30[foobar_23, 1:foobar_12 - 1] = 2 * foobar_28[foobar_23, 1:foobar_12 - 1] - (foobar_28[foobar_23, 1:foobar_12 - 1] - 2 * foobar_20 * foobar_15[foobar_23, 1:foobar_12 - 1]) + foobar_5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23 + 1, 1:foobar_12 - 1]) * (foobar_28[foobar_23 + 1, 1:foobar_12 - 1] - foobar_28[foobar_23, 1:foobar_12 - 1]) + foobar_6 * (0.5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23, 2:foobar_12]) * (foobar_28[foobar_23, 2:foobar_12] - foobar_28[foobar_23, 1:foobar_12 - 1]) - 0.5 * (foobar_27[foobar_23, 0:foobar_12 - 2] + foobar_27[foobar_23, 1:foobar_12 - 1]) * (foobar_28[foobar_23, 1:foobar_12 - 1] - foobar_28[foobar_23, 0:foobar_12 - 2]))\n
@@ -20363,13 +19890,13 @@
             foobar_30[:, 0] = 0\n
             foobar_30[:, -1] = 0\n
         elif foobar_18 == 2:\n
-            foobar_23, foobar_24 = (0, 0)\n
+            (foobar_23, foobar_24) = (0, 0)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 + 1]) * (foobar_28[foobar_23, foobar_24 + 1] - foobar_28[foobar_23, foobar_24])\n
-            foobar_23, foobar_24 = (0, foobar_12)\n
+            (foobar_23, foobar_24) = (0, foobar_12)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 + 1, foobar_24]) * (foobar_28[foobar_23 + 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
-            foobar_23, foobar_24 = (foobar_11, 0)\n
+            (foobar_23, foobar_24) = (foobar_11, 0)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
-            foobar_23, foobar_24 = (foobar_11, foobar_12)\n
+            (foobar_23, foobar_24) = (foobar_11, foobar_12)\n
             foobar_30[foobar_23, foobar_24] = 2 * foobar_28[foobar_23, foobar_24] - foobar_29[foobar_23, foobar_24] + foobar_5 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23 - 1, foobar_24]) * (foobar_28[foobar_23 - 1, foobar_24] - foobar_28[foobar_23, foobar_24]) + foobar_6 * (foobar_27[foobar_23, foobar_24] + foobar_27[foobar_23, foobar_24 - 1]) * (foobar_28[foobar_23, foobar_24 - 1] - foobar_28[foobar_23, foobar_24])\n
             foobar_23 = 0\n
             foobar_30[foobar_23, 1:foobar_12 - 1] = 2 * foobar_28[foobar_23, 1:foobar_12 - 1] - foobar_29[foobar_23, 1:foobar_12 - 1] + foobar_5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23 + 1, 1:foobar_12 - 1]) * (foobar_28[foobar_23 + 1, 1:foobar_12 - 1] - foobar_28[foobar_23, 1:foobar_12 - 1]) + foobar_6 * (0.5 * (foobar_27[foobar_23, 1:foobar_12 - 1] + foobar_27[foobar_23, 2:foobar_12]) * (foobar_28[foobar_23, 2:foobar_12] - foobar_28[foobar_23, 1:foobar_12 - 1]) - 0.5 * (foobar_27[foobar_23, 0:foobar_12 - 2] + foobar_27[foobar_23, foobar_24]) * (foobar_28[foobar_23, 1:foobar_12 - 1] - foobar_28[foobar_23, 0:foobar_12 - 2]))\n
@@ -20397,7 +19924,7 @@
         <v>125</v>
       </c>
       <c r="D98" t="n">
-        <v>16198</v>
+        <v>16214</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -20445,12 +19972,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -20593,12 +20115,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -20703,12 +20220,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -20746,14 +20258,14 @@
     foobar_20 = np.linspace(0, foobar_3, foobar_4, endpoint=False)\n
     foobar_15 = np.exp(-50 * (foobar_20 - foobar_3 / 2) ** 2)\n
     foobar_18 = np.zeros_like(foobar_20)\n
-    foobar_20, foobar_12, foobar_10 = fn1(foobar_15, foobar_18, foobar_3, T=5, dt=0.05, c=foobar_6)</t>
+    (foobar_20, foobar_12, foobar_10) = fn1(foobar_15, foobar_18, foobar_3, T=5, dt=0.05, c=foobar_6)</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>27</v>
       </c>
       <c r="D101" t="n">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -20801,12 +20313,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -20895,12 +20402,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -20994,12 +20496,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -21091,12 +20588,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -21190,12 +20682,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -21289,12 +20776,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -21397,12 +20879,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -21489,12 +20966,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -21572,12 +21044,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -21601,7 +21068,7 @@
 foobar_7 = 2 / (foobar_13 - 1)\n
 foobar_22 = numpy.linspace(0, 2, foobar_12)\n
 foobar_23 = numpy.linspace(0, 2, foobar_13)\n
-foobar_1, foobar_2 = numpy.meshgrid(foobar_22, foobar_23)\n
+(foobar_1, foobar_2) = numpy.meshgrid(foobar_22, foobar_23)\n
 foobar_17 = 1\n
 foobar_11 = 0.1\n
 foobar_5 = 0.001\n
@@ -21651,14 +21118,14 @@
 foobar_14 = numpy.zeros((foobar_13, foobar_12))\n
 foobar_3 = numpy.zeros((foobar_13, foobar_12))\n
 foobar_10 = 700\n
-foobar_18, foobar_20, foobar_14 = fn3(foobar_10, foobar_18, foobar_20, foobar_5, foobar_6, foobar_7, foobar_14, foobar_17, foobar_11)</t>
+(foobar_18, foobar_20, foobar_14) = fn3(foobar_10, foobar_18, foobar_20, foobar_5, foobar_6, foobar_7, foobar_14, foobar_17, foobar_11)</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>63</v>
       </c>
       <c r="D110" t="n">
-        <v>4214</v>
+        <v>4218</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -21706,12 +21173,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21214,7 @@
 foobar_8 = 2 / (foobar_13 - 1)\n
 foobar_24 = numpy.linspace(0, 2, foobar_12)\n
 foobar_25 = numpy.linspace(0, 2, foobar_13)\n
-foobar_2, foobar_3 = numpy.meshgrid(foobar_24, foobar_25)\n
+(foobar_2, foobar_3) = numpy.meshgrid(foobar_24, foobar_25)\n
 foobar_17 = 1\n
 foobar_11 = 0.1\n
 foobar_1 = 1\n
@@ -21789,7 +21251,7 @@
         <v>60</v>
       </c>
       <c r="D111" t="n">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -21837,12 +21299,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21339,7 @@
 def fn1(foobar_1, foobar_7):\n
     foobar_19 = np.ogrid[foobar_1.local_slice(False)]\n
     foobar_10 = foobar_1.global_shape()\n
-    foobar_19 = [np.broadcast_to(foobar_39 * foobar_7[foobar_26] / foobar_10[foobar_26], foobar_1.shape(False)) for foobar_26, foobar_39 in enumerate(foobar_19)]\n
+    foobar_19 = [np.broadcast_to(foobar_39 * foobar_7[foobar_26] / foobar_10[foobar_26], foobar_1.shape(False)) for (foobar_26, foobar_39) in enumerate(foobar_19)]\n
     return foobar_19\n
 \n
 def fn2(foobar_1, foobar_7):\n
@@ -21890,10 +21347,10 @@
     foobar_10 = foobar_1.global_shape()\n
     foobar_28 = [np.fft.fftfreq(foobar_30, 1.0 / foobar_30).astype(int) for foobar_30 in foobar_10[:-1]]\n
     foobar_28.append(np.fft.rfftfreq(foobar_10[-1], 1.0 / foobar_10[-1]).astype(int))\n
-    foobar_3 = [foobar_29[foobar_35] for foobar_29, foobar_35 in zip(foobar_28, foobar_34)]\n
+    foobar_3 = [foobar_29[foobar_35] for (foobar_29, foobar_35) in zip(foobar_28, foobar_34)]\n
     foobar_6 = np.meshgrid(*foobar_3, indexing='ij', sparse=True)\n
     foobar_8 = 2 * np.pi / foobar_7\n
-    return [np.broadcast_to(foobar_28 * foobar_8[foobar_26], foobar_1.shape(True)) for foobar_26, foobar_28 in enumerate(foobar_6)]\n
+    return [np.broadcast_to(foobar_28 * foobar_8[foobar_26], foobar_1.shape(True)) for (foobar_26, foobar_28) in enumerate(foobar_6)]\n
 foobar_19 = fn1(foobar_1, foobar_7)\n
 foobar_3 = fn2(foobar_1, foobar_7)\n
 foobar_3 = np.array(foobar_3).astype(float)\n
@@ -21952,7 +21409,7 @@
         <v>92</v>
       </c>
       <c r="D112" t="n">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -22000,12 +21457,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
@@ -22048,15 +21500,15 @@
 def fn4(foobar_27, foobar_1, foobar_2, foobar_33, foobar_45=4):\n
     foobar_23 = grids.Grid((foobar_1, foobar_2), domain=((0, 2 * jnp.pi), (0, 2 * jnp.pi)))\n
     foobar_56 = initial_conditions.filtered_velocity_field(foobar_27, foobar_23, maximum_velocity=foobar_33, peak_wavenumber=foobar_45)\n
-    foobar_59, foobar_61 = (foobar_56[0].data, foobar_56[1].data)\n
-    foobar_29, foobar_30 = fn1(foobar_1, foobar_2)\n
+    (foobar_59, foobar_61) = (foobar_56[0].data, foobar_56[1].data)\n
+    (foobar_29, foobar_30) = fn1(foobar_1, foobar_2)\n
     foobar_60 = jnp.fft.rfftn(foobar_59)\n
     foobar_62 = jnp.fft.rfftn(foobar_61)\n
     foobar_42 = 2j * jnp.pi * (foobar_29 * foobar_62 - foobar_30 * foobar_60)\n
     return jnp.fft.irfftn(foobar_42, s=(foobar_1, foobar_2))\n
 \n
 def fn5(foobar_58, foobar_29, foobar_30, foobar_16, foobar_1, foobar_2):\n
-    foobar_60, foobar_62 = fn3(foobar_58, foobar_29, foobar_30)\n
+    (foobar_60, foobar_62) = fn3(foobar_58, foobar_29, foobar_30)\n
     foobar_59 = jnp.fft.irfftn(foobar_60, s=(foobar_1, foobar_2))\n
     foobar_61 = jnp.fft.irfftn(foobar_62, s=(foobar_1, foobar_2))\n
     foobar_20 = 2j * jnp.pi * foobar_29 * foobar_58\n
@@ -22086,26 +21538,26 @@
     foobar_49 = jnp.array(foobar_48)\n
     foobar_15 = foobar_49[1] - foobar_49[0]\n
     foobar_36 = len(foobar_49) - 1\n
-    foobar_29, foobar_30 = fn1(foobar_1, foobar_2)\n
+    (foobar_29, foobar_30) = fn1(foobar_1, foobar_2)\n
     foobar_16 = fn2(foobar_1, foobar_2)\n
     foobar_31 = (2j * jnp.pi) ** 2 * (foobar_29 ** 2 + foobar_30 ** 2)\n
     foobar_32 = foobar_57 * foobar_31 - foobar_14\n
-    foobar_27, foobar_26 = random.split(foobar_27)\n
+    (foobar_27, foobar_26) = random.split(foobar_27)\n
     foobar_40 = foobar_17 if foobar_17 is not None else fn4(foobar_26, foobar_1, foobar_2, foobar_33)\n
     foobar_41 = jnp.fft.rfftn(foobar_40)\n
     foobar_47 = foobar_36 // (foobar_50 - 1)\n
 \n
     def fn9(foobar_12, foobar_5):\n
-        foobar_42, foobar_27 = foobar_12\n
+        (foobar_42, foobar_27) = foobar_12\n
 \n
         def fn10(foobar_12, foobar_5):\n
-            foobar_42, foobar_27 = foobar_12\n
-            foobar_27, foobar_5 = random.split(foobar_27)\n
+            (foobar_42, foobar_27) = foobar_12\n
+            (foobar_27, foobar_5) = random.split(foobar_27)\n
             foobar_43 = fn6(foobar_42, foobar_29, foobar_30, foobar_16, foobar_1, foobar_2, foobar_32, foobar_15)\n
             return ((foobar_43, foobar_27), None)\n
-        (foobar_43, foobar_27), foobar_5 = lax.scan(fn10, (foobar_42, foobar_27), None, length=foobar_47)\n
+        ((foobar_43, foobar_27), foobar_5) = lax.scan(fn10, (foobar_42, foobar_27), None, length=foobar_47)\n
         return ((foobar_43, foobar_27), foobar_43)\n
-    (foobar_5, foobar_5), foobar_53 = lax.scan(fn9, (foobar_41, foobar_27), None, length=foobar_50 - 1)\n
+    ((foobar_5, foobar_5), foobar_53) = lax.scan(fn9, (foobar_41, foobar_27), None, length=foobar_50 - 1)\n
     foobar_53 = jnp.concatenate([foobar_41[None], foobar_53], axis=0)\n
     if foobar_51 is not None and foobar_51 != foobar_1:\n
         foobar_3 = foobar_51\n
@@ -22137,7 +21589,7 @@
         <v>114</v>
       </c>
       <c r="D113" t="n">
-        <v>6739</v>
+        <v>6759</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -22185,12 +21637,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>CorrComm</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NoComm_CorrVar</t>
         </is>
       </c>
     </row>
